--- a/Data/in Use/event_skill.xlsx
+++ b/Data/in Use/event_skill.xlsx
@@ -3,15 +3,17 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Sheet1!$A$1:$Z$481</definedName>
+  </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1138" uniqueCount="344">
   <si>
     <t>tour</t>
   </si>
@@ -292,15 +294,24 @@
     <t>Chicago</t>
   </si>
   <si>
+    <t>–0.09</t>
+  </si>
+  <si>
     <t>Bangkok</t>
   </si>
   <si>
     <t>Jeddah</t>
   </si>
   <si>
+    <t>–0.02</t>
+  </si>
+  <si>
     <t>Mayakoba</t>
   </si>
   <si>
+    <t>–0.03</t>
+  </si>
+  <si>
     <t>Tucson</t>
   </si>
   <si>
@@ -310,6 +321,9 @@
     <t>Adelaide</t>
   </si>
   <si>
+    <t>–0.10</t>
+  </si>
+  <si>
     <t>Singapore</t>
   </si>
   <si>
@@ -325,7 +339,7 @@
     <t>Greenbrier</t>
   </si>
   <si>
-    <t>–0.03</t>
+    <t>–0.07</t>
   </si>
   <si>
     <t>Las Vegas</t>
@@ -334,9 +348,6 @@
     <t>–0.01</t>
   </si>
   <si>
-    <t>–0.02</t>
-  </si>
-  <si>
     <t>Hong Kong</t>
   </si>
   <si>
@@ -349,9 +360,6 @@
     <t>–0.08</t>
   </si>
   <si>
-    <t>–0.10</t>
-  </si>
-  <si>
     <t>Houston</t>
   </si>
   <si>
@@ -364,12 +372,6 @@
     <t>United Kingdom</t>
   </si>
   <si>
-    <t>–0.07</t>
-  </si>
-  <si>
-    <t>–0.09</t>
-  </si>
-  <si>
     <t>MAJ</t>
   </si>
   <si>
@@ -701,16 +703,359 @@
   </si>
   <si>
     <t>–0.54</t>
+  </si>
+  <si>
+    <t>2025137</t>
+  </si>
+  <si>
+    <t>2025136</t>
+  </si>
+  <si>
+    <t>2025135</t>
+  </si>
+  <si>
+    <t>DP World India Championship</t>
+  </si>
+  <si>
+    <t>2025141</t>
+  </si>
+  <si>
+    <t>Open de España presented by Madrid</t>
+  </si>
+  <si>
+    <t>2025134</t>
+  </si>
+  <si>
+    <t>2025133</t>
+  </si>
+  <si>
+    <t>2025131</t>
+  </si>
+  <si>
+    <t>2025130</t>
+  </si>
+  <si>
+    <t>2025129</t>
+  </si>
+  <si>
+    <t>2025128</t>
+  </si>
+  <si>
+    <t>2025127</t>
+  </si>
+  <si>
+    <t>2025126</t>
+  </si>
+  <si>
+    <t>Nexo Championship</t>
+  </si>
+  <si>
+    <t>2025125</t>
+  </si>
+  <si>
+    <t>2025120</t>
+  </si>
+  <si>
+    <t>Italian Open</t>
+  </si>
+  <si>
+    <t>2025119</t>
+  </si>
+  <si>
+    <t>2025118</t>
+  </si>
+  <si>
+    <t>Austrian Alpine Open presented by SalzburgerLand</t>
+  </si>
+  <si>
+    <t>2025143</t>
+  </si>
+  <si>
+    <t>2025117</t>
+  </si>
+  <si>
+    <t>Turkish Airlines Open</t>
+  </si>
+  <si>
+    <t>2025140</t>
+  </si>
+  <si>
+    <t>Hainan Classic</t>
+  </si>
+  <si>
+    <t>2025139</t>
+  </si>
+  <si>
+    <t>2025115</t>
+  </si>
+  <si>
+    <t>2025113</t>
+  </si>
+  <si>
+    <t>2025112</t>
+  </si>
+  <si>
+    <t>2025111</t>
+  </si>
+  <si>
+    <t>2025109</t>
+  </si>
+  <si>
+    <t>2025142</t>
+  </si>
+  <si>
+    <t>Bapco Energies Bahrain Championship</t>
+  </si>
+  <si>
+    <t>2025108</t>
+  </si>
+  <si>
+    <t>2025107</t>
+  </si>
+  <si>
+    <t>2025106</t>
+  </si>
+  <si>
+    <t>2025104</t>
+  </si>
+  <si>
+    <t>2025103</t>
+  </si>
+  <si>
+    <t>2025102</t>
+  </si>
+  <si>
+    <t>2025101</t>
+  </si>
+  <si>
+    <t>BMW Australian PGA Championship</t>
+  </si>
+  <si>
+    <t>2025100</t>
+  </si>
+  <si>
+    <t>Indianapolis</t>
+  </si>
+  <si>
+    <t>1032</t>
+  </si>
+  <si>
+    <t>1005</t>
+  </si>
+  <si>
+    <t>1025</t>
+  </si>
+  <si>
+    <t>1024</t>
+  </si>
+  <si>
+    <t>Dallas</t>
+  </si>
+  <si>
+    <t>1031</t>
+  </si>
+  <si>
+    <t>Virginia</t>
+  </si>
+  <si>
+    <t>1030</t>
+  </si>
+  <si>
+    <t>Korea</t>
+  </si>
+  <si>
+    <t>1029</t>
+  </si>
+  <si>
+    <t>Mexico City</t>
+  </si>
+  <si>
+    <t>1028</t>
+  </si>
+  <si>
+    <t>1021</t>
+  </si>
+  <si>
+    <t>1013</t>
+  </si>
+  <si>
+    <t>1020</t>
+  </si>
+  <si>
+    <t>1012</t>
+  </si>
+  <si>
+    <t>Riyadh</t>
+  </si>
+  <si>
+    <t>1027</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>478</t>
+  </si>
+  <si>
+    <t>493</t>
+  </si>
+  <si>
+    <t>528</t>
+  </si>
+  <si>
+    <t>457</t>
+  </si>
+  <si>
+    <t>Bank of Utah Championship</t>
+  </si>
+  <si>
+    <t>554</t>
+  </si>
+  <si>
+    <t>Baycurrent Classic</t>
+  </si>
+  <si>
+    <t>527</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>464</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>525</t>
+  </si>
+  <si>
+    <t>518</t>
+  </si>
+  <si>
+    <t>541</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>Rocket Classic</t>
+  </si>
+  <si>
+    <t>524</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>ONEflight Myrtle Beach Classic</t>
+  </si>
+  <si>
+    <t>553</t>
+  </si>
+  <si>
+    <t>Truist Championship</t>
+  </si>
+  <si>
+    <t>480</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>522</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>475</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>483</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Mexico Open at VidantaWorld</t>
+  </si>
+  <si>
+    <t>540</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>EURO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
+    <numFmt numFmtId="165" formatCode="M/d/yyyy"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -721,6 +1066,10 @@
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -737,7 +1086,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -746,6 +1095,15 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -757,6 +1115,10 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2713,22 +3075,22 @@
         <v>87</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C77" s="2">
-        <v>44745.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D77" s="1">
-        <v>1002.0</v>
+        <v>1001.0</v>
       </c>
       <c r="E77" s="1">
-        <v>-0.36</v>
+        <v>-0.02</v>
       </c>
       <c r="F77" s="1">
-        <v>0.8</v>
+        <v>0.851664</v>
       </c>
       <c r="G77" s="1">
-        <v>2022.0</v>
+        <v>2023.0</v>
       </c>
     </row>
     <row r="78">
@@ -2736,19 +3098,19 @@
         <v>87</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C78" s="2">
-        <v>44773.0</v>
+        <v>44745.0</v>
       </c>
       <c r="D78" s="1">
-        <v>1003.0</v>
+        <v>1002.0</v>
       </c>
       <c r="E78" s="1">
-        <v>-0.25</v>
+        <v>-0.36</v>
       </c>
       <c r="F78" s="1">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="G78" s="1">
         <v>2022.0</v>
@@ -2759,19 +3121,19 @@
         <v>87</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C79" s="2">
-        <v>44808.0</v>
+        <v>44773.0</v>
       </c>
       <c r="D79" s="1">
-        <v>1004.0</v>
+        <v>1003.0</v>
       </c>
       <c r="E79" s="1">
-        <v>-0.13</v>
+        <v>-0.25</v>
       </c>
       <c r="F79" s="1">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="G79" s="1">
         <v>2022.0</v>
@@ -2782,22 +3144,22 @@
         <v>87</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C80" s="2">
-        <v>44822.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D80" s="1">
-        <v>1005.0</v>
+        <v>1003.0</v>
       </c>
       <c r="E80" s="1">
         <v>-0.05</v>
       </c>
       <c r="F80" s="1">
-        <v>0.87</v>
+        <v>0.842358</v>
       </c>
       <c r="G80" s="1">
-        <v>2022.0</v>
+        <v>2023.0</v>
       </c>
     </row>
     <row r="81">
@@ -2805,19 +3167,19 @@
         <v>87</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C81" s="2">
-        <v>44843.0</v>
+        <v>44808.0</v>
       </c>
       <c r="D81" s="1">
-        <v>1006.0</v>
+        <v>1004.0</v>
       </c>
       <c r="E81" s="1">
-        <v>-0.07</v>
+        <v>-0.13</v>
       </c>
       <c r="F81" s="1">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="G81" s="1">
         <v>2022.0</v>
@@ -2828,19 +3190,19 @@
         <v>87</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C82" s="2">
-        <v>44850.0</v>
+        <v>44822.0</v>
       </c>
       <c r="D82" s="1">
-        <v>1007.0</v>
+        <v>1005.0</v>
       </c>
       <c r="E82" s="1">
-        <v>-0.09</v>
+        <v>-0.05</v>
       </c>
       <c r="F82" s="1">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="G82" s="1">
         <v>2022.0</v>
@@ -2851,19 +3213,19 @@
         <v>87</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C83" s="2">
-        <v>44983.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D83" s="1">
-        <v>1009.0</v>
+        <v>1005.0</v>
       </c>
       <c r="E83" s="1">
-        <v>0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="F83" s="1">
-        <v>0.84</v>
+        <v>0.833339</v>
       </c>
       <c r="G83" s="1">
         <v>2023.0</v>
@@ -2874,22 +3236,22 @@
         <v>87</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C84" s="2">
-        <v>45004.0</v>
+        <v>45550.0</v>
       </c>
       <c r="D84" s="1">
-        <v>1010.0</v>
-      </c>
-      <c r="E84" s="1">
-        <v>0.01</v>
+        <v>1005.0</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="F84" s="1">
-        <v>0.855872</v>
+        <v>0.8711137834</v>
       </c>
       <c r="G84" s="1">
-        <v>2023.0</v>
+        <v>2024.0</v>
       </c>
     </row>
     <row r="85">
@@ -2897,22 +3259,22 @@
         <v>87</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C85" s="2">
-        <v>45018.0</v>
+        <v>44843.0</v>
       </c>
       <c r="D85" s="1">
-        <v>1011.0</v>
+        <v>1006.0</v>
       </c>
       <c r="E85" s="1">
-        <v>-0.03</v>
+        <v>-0.07</v>
       </c>
       <c r="F85" s="1">
-        <v>0.852211</v>
+        <v>0.86</v>
       </c>
       <c r="G85" s="1">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
     </row>
     <row r="86">
@@ -2920,22 +3282,22 @@
         <v>87</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C86" s="2">
-        <v>45039.0</v>
+        <v>44850.0</v>
       </c>
       <c r="D86" s="1">
-        <v>1012.0</v>
+        <v>1007.0</v>
       </c>
       <c r="E86" s="1">
-        <v>-0.01</v>
+        <v>-0.09</v>
       </c>
       <c r="F86" s="1">
-        <v>0.841147</v>
+        <v>0.85</v>
       </c>
       <c r="G86" s="1">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
     </row>
     <row r="87">
@@ -2943,19 +3305,19 @@
         <v>87</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C87" s="2">
-        <v>45046.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D87" s="1">
-        <v>1013.0</v>
+        <v>1007.0</v>
       </c>
       <c r="E87" s="1">
-        <v>-0.03</v>
+        <v>-0.12</v>
       </c>
       <c r="F87" s="1">
-        <v>0.846034</v>
+        <v>0.833852</v>
       </c>
       <c r="G87" s="1">
         <v>2023.0</v>
@@ -2966,22 +3328,22 @@
         <v>87</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C88" s="2">
-        <v>45060.0</v>
+        <v>45354.0</v>
       </c>
       <c r="D88" s="1">
-        <v>1014.0</v>
-      </c>
-      <c r="E88" s="1">
-        <v>-0.04</v>
+        <v>1007.0</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="F88" s="1">
-        <v>0.849435</v>
+        <v>0.86846626</v>
       </c>
       <c r="G88" s="1">
-        <v>2023.0</v>
+        <v>2024.0</v>
       </c>
     </row>
     <row r="89">
@@ -2989,19 +3351,19 @@
         <v>87</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C89" s="2">
-        <v>45074.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D89" s="1">
-        <v>1015.0</v>
+        <v>1009.0</v>
       </c>
       <c r="E89" s="1">
-        <v>-0.03</v>
+        <v>0.05</v>
       </c>
       <c r="F89" s="1">
-        <v>0.845264</v>
+        <v>0.84</v>
       </c>
       <c r="G89" s="1">
         <v>2023.0</v>
@@ -3012,22 +3374,22 @@
         <v>87</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C90" s="2">
-        <v>45109.0</v>
+        <v>45326.0</v>
       </c>
       <c r="D90" s="1">
-        <v>1016.0</v>
-      </c>
-      <c r="E90" s="1">
-        <v>-0.03</v>
+        <v>1009.0</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="F90" s="1">
-        <v>0.852927</v>
+        <v>0.856516841</v>
       </c>
       <c r="G90" s="1">
-        <v>2023.0</v>
+        <v>2024.0</v>
       </c>
     </row>
     <row r="91">
@@ -3035,19 +3397,19 @@
         <v>87</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="C91" s="2">
-        <v>45116.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D91" s="1">
-        <v>1001.0</v>
+        <v>1010.0</v>
       </c>
       <c r="E91" s="1">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F91" s="1">
-        <v>0.851664</v>
+        <v>0.855872</v>
       </c>
       <c r="G91" s="1">
         <v>2023.0</v>
@@ -3058,19 +3420,19 @@
         <v>87</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C92" s="2">
-        <v>45144.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D92" s="1">
-        <v>1017.0</v>
+        <v>1011.0</v>
       </c>
       <c r="E92" s="1">
-        <v>-0.07</v>
+        <v>-0.03</v>
       </c>
       <c r="F92" s="1">
-        <v>0.847174</v>
+        <v>0.852211</v>
       </c>
       <c r="G92" s="1">
         <v>2023.0</v>
@@ -3081,19 +3443,19 @@
         <v>87</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="C93" s="2">
-        <v>45151.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D93" s="1">
-        <v>1003.0</v>
+        <v>1012.0</v>
       </c>
       <c r="E93" s="1">
-        <v>-0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="F93" s="1">
-        <v>0.842358</v>
+        <v>0.841147</v>
       </c>
       <c r="G93" s="1">
         <v>2023.0</v>
@@ -3104,22 +3466,22 @@
         <v>87</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C94" s="2">
-        <v>45193.0</v>
+        <v>45410.0</v>
       </c>
       <c r="D94" s="1">
-        <v>1005.0</v>
-      </c>
-      <c r="E94" s="1">
-        <v>-0.1</v>
+        <v>1012.0</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="F94" s="1">
-        <v>0.833339</v>
+        <v>0.8630323332</v>
       </c>
       <c r="G94" s="1">
-        <v>2023.0</v>
+        <v>2024.0</v>
       </c>
     </row>
     <row r="95">
@@ -3127,19 +3489,19 @@
         <v>87</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="C95" s="2">
-        <v>45214.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D95" s="1">
-        <v>1007.0</v>
+        <v>1013.0</v>
       </c>
       <c r="E95" s="1">
-        <v>-0.12</v>
+        <v>-0.03</v>
       </c>
       <c r="F95" s="1">
-        <v>0.833852</v>
+        <v>0.846034</v>
       </c>
       <c r="G95" s="1">
         <v>2023.0</v>
@@ -3150,19 +3512,19 @@
         <v>87</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="C96" s="2">
-        <v>45326.0</v>
+        <v>45417.0</v>
       </c>
       <c r="D96" s="1">
-        <v>1009.0</v>
+        <v>1013.0</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F96" s="1">
-        <v>0.856516841</v>
+        <v>0.8620134225</v>
       </c>
       <c r="G96" s="1">
         <v>2024.0</v>
@@ -3173,22 +3535,22 @@
         <v>87</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C97" s="2">
-        <v>45332.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D97" s="1">
-        <v>1019.0</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>106</v>
+        <v>1014.0</v>
+      </c>
+      <c r="E97" s="1">
+        <v>-0.04</v>
       </c>
       <c r="F97" s="1">
-        <v>0.8660874464</v>
+        <v>0.849435</v>
       </c>
       <c r="G97" s="1">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
     </row>
     <row r="98">
@@ -3196,22 +3558,22 @@
         <v>87</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="C98" s="2">
-        <v>45354.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D98" s="1">
-        <v>1007.0</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>107</v>
+        <v>1015.0</v>
+      </c>
+      <c r="E98" s="1">
+        <v>-0.03</v>
       </c>
       <c r="F98" s="1">
-        <v>0.86846626</v>
+        <v>0.845264</v>
       </c>
       <c r="G98" s="1">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
     </row>
     <row r="99">
@@ -3219,22 +3581,22 @@
         <v>87</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C99" s="2">
-        <v>45361.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D99" s="1">
-        <v>1020.0</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>109</v>
+        <v>1016.0</v>
+      </c>
+      <c r="E99" s="1">
+        <v>-0.03</v>
       </c>
       <c r="F99" s="1">
-        <v>0.8625373633</v>
+        <v>0.852927</v>
       </c>
       <c r="G99" s="1">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
     </row>
     <row r="100">
@@ -3242,22 +3604,22 @@
         <v>87</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C100" s="2">
-        <v>45389.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D100" s="1">
-        <v>1021.0</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>111</v>
+        <v>1017.0</v>
+      </c>
+      <c r="E100" s="1">
+        <v>-0.07</v>
       </c>
       <c r="F100" s="1">
-        <v>0.8669994972</v>
+        <v>0.847174</v>
       </c>
       <c r="G100" s="1">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
     </row>
     <row r="101">
@@ -3265,19 +3627,19 @@
         <v>87</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C101" s="2">
-        <v>45410.0</v>
+        <v>45522.0</v>
       </c>
       <c r="D101" s="1">
-        <v>1012.0</v>
+        <v>1017.0</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F101" s="1">
-        <v>0.8630323332</v>
+        <v>0.8743566454</v>
       </c>
       <c r="G101" s="1">
         <v>2024.0</v>
@@ -3288,19 +3650,19 @@
         <v>87</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="C102" s="2">
-        <v>45417.0</v>
+        <v>45332.0</v>
       </c>
       <c r="D102" s="1">
-        <v>1013.0</v>
+        <v>1019.0</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F102" s="1">
-        <v>0.8620134225</v>
+        <v>0.8660874464</v>
       </c>
       <c r="G102" s="1">
         <v>2024.0</v>
@@ -3311,19 +3673,19 @@
         <v>87</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C103" s="2">
-        <v>45452.0</v>
+        <v>45361.0</v>
       </c>
       <c r="D103" s="1">
-        <v>1022.0</v>
+        <v>1020.0</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>112</v>
       </c>
       <c r="F103" s="1">
-        <v>0.872720443</v>
+        <v>0.8625373633</v>
       </c>
       <c r="G103" s="1">
         <v>2024.0</v>
@@ -3334,19 +3696,19 @@
         <v>87</v>
       </c>
       <c r="B104" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C104" s="2">
+        <v>45389.0</v>
+      </c>
+      <c r="D104" s="1">
+        <v>1021.0</v>
+      </c>
+      <c r="E104" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C104" s="2">
-        <v>45466.0</v>
-      </c>
-      <c r="D104" s="1">
-        <v>1023.0</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>112</v>
-      </c>
       <c r="F104" s="1">
-        <v>0.86246825</v>
+        <v>0.8669994972</v>
       </c>
       <c r="G104" s="1">
         <v>2024.0</v>
@@ -3360,16 +3722,16 @@
         <v>115</v>
       </c>
       <c r="C105" s="2">
-        <v>45487.0</v>
+        <v>45452.0</v>
       </c>
       <c r="D105" s="1">
-        <v>1024.0</v>
+        <v>1022.0</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="F105" s="1">
-        <v>0.8641834255</v>
+        <v>0.872720443</v>
       </c>
       <c r="G105" s="1">
         <v>2024.0</v>
@@ -3383,16 +3745,16 @@
         <v>116</v>
       </c>
       <c r="C106" s="2">
-        <v>45501.0</v>
+        <v>45466.0</v>
       </c>
       <c r="D106" s="1">
-        <v>1025.0</v>
+        <v>1023.0</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="F106" s="1">
-        <v>0.8747876065</v>
+        <v>0.86246825</v>
       </c>
       <c r="G106" s="1">
         <v>2024.0</v>
@@ -3403,19 +3765,19 @@
         <v>87</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="C107" s="2">
-        <v>45522.0</v>
+        <v>45487.0</v>
       </c>
       <c r="D107" s="1">
-        <v>1017.0</v>
+        <v>1024.0</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F107" s="1">
-        <v>0.8743566454</v>
+        <v>0.8641834255</v>
       </c>
       <c r="G107" s="1">
         <v>2024.0</v>
@@ -3426,19 +3788,19 @@
         <v>87</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="C108" s="2">
-        <v>45550.0</v>
+        <v>45501.0</v>
       </c>
       <c r="D108" s="1">
-        <v>1005.0</v>
+        <v>1025.0</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F108" s="1">
-        <v>0.8711137834</v>
+        <v>0.8747876065</v>
       </c>
       <c r="G108" s="1">
         <v>2024.0</v>
@@ -3941,7 +4303,7 @@
         <v>26.0</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="F130" s="1">
         <v>0.9649859375</v>
@@ -3964,7 +4326,7 @@
         <v>100.0</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="F131" s="1">
         <v>0.9656538163</v>
@@ -8886,7 +9248,7 @@
         <v>6.0</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="F345" s="1">
         <v>0.9197953776</v>
@@ -8909,7 +9271,7 @@
         <v>2.0</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F346" s="1">
         <v>0.934353535</v>
@@ -8932,7 +9294,7 @@
         <v>4.0</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="F347" s="1">
         <v>0.9262495656</v>
@@ -9323,7 +9685,7 @@
         <v>21.0</v>
       </c>
       <c r="E364" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="F364" s="1">
         <v>0.932596131</v>
@@ -9461,7 +9823,7 @@
         <v>541.0</v>
       </c>
       <c r="E370" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="F370" s="1">
         <v>0.9473937781</v>
@@ -9861,7 +10223,2174 @@
         <v>2024.0</v>
       </c>
     </row>
+    <row r="388">
+      <c r="A388" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B388" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C388" s="4">
+        <v>45977.0</v>
+      </c>
+      <c r="D388" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="E388" s="5">
+        <v>0.24</v>
+      </c>
+      <c r="F388" s="5">
+        <v>0.8988907283</v>
+      </c>
+      <c r="G388" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B389" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C389" s="4">
+        <v>45970.0</v>
+      </c>
+      <c r="D389" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E389" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="F389" s="5">
+        <v>0.8877776172</v>
+      </c>
+      <c r="G389" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B390" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C390" s="4">
+        <v>45956.0</v>
+      </c>
+      <c r="D390" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="E390" s="5">
+        <v>-0.91</v>
+      </c>
+      <c r="F390" s="5">
+        <v>0.7981371143</v>
+      </c>
+      <c r="G390" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B391" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="C391" s="4">
+        <v>45949.0</v>
+      </c>
+      <c r="D391" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E391" s="5">
+        <v>-1.19</v>
+      </c>
+      <c r="F391" s="5">
+        <v>0.8550334944</v>
+      </c>
+      <c r="G391" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B392" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C392" s="4">
+        <v>45942.0</v>
+      </c>
+      <c r="D392" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="E392" s="5">
+        <v>-0.81</v>
+      </c>
+      <c r="F392" s="5">
+        <v>0.8439533141</v>
+      </c>
+      <c r="G392" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B393" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C393" s="4">
+        <v>45935.0</v>
+      </c>
+      <c r="D393" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="E393" s="5">
+        <v>-0.92</v>
+      </c>
+      <c r="F393" s="5">
+        <v>0.87314616</v>
+      </c>
+      <c r="G393" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B394" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C394" s="4">
+        <v>45921.0</v>
+      </c>
+      <c r="D394" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E394" s="5">
+        <v>-1.01</v>
+      </c>
+      <c r="F394" s="5">
+        <v>0.8293911566</v>
+      </c>
+      <c r="G394" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B395" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C395" s="4">
+        <v>45914.0</v>
+      </c>
+      <c r="D395" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E395" s="5">
+        <v>-0.26</v>
+      </c>
+      <c r="F395" s="5">
+        <v>0.9286506065</v>
+      </c>
+      <c r="G395" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B396" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C396" s="4">
+        <v>45907.0</v>
+      </c>
+      <c r="D396" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="E396" s="5">
+        <v>-0.79</v>
+      </c>
+      <c r="F396" s="5">
+        <v>0.8583952267</v>
+      </c>
+      <c r="G396" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B397" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C397" s="4">
+        <v>45900.0</v>
+      </c>
+      <c r="D397" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="E397" s="5">
+        <v>-1.13</v>
+      </c>
+      <c r="F397" s="5">
+        <v>0.8467382543</v>
+      </c>
+      <c r="G397" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B398" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C398" s="4">
+        <v>45893.0</v>
+      </c>
+      <c r="D398" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E398" s="5">
+        <v>-0.95</v>
+      </c>
+      <c r="F398" s="5">
+        <v>0.837769336</v>
+      </c>
+      <c r="G398" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B399" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C399" s="4">
+        <v>45886.0</v>
+      </c>
+      <c r="D399" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="E399" s="5">
+        <v>-1.38</v>
+      </c>
+      <c r="F399" s="5">
+        <v>0.7620212221</v>
+      </c>
+      <c r="G399" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B400" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C400" s="4">
+        <v>45879.0</v>
+      </c>
+      <c r="D400" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="E400" s="5">
+        <v>-1.34</v>
+      </c>
+      <c r="F400" s="5">
+        <v>0.742111613</v>
+      </c>
+      <c r="G400" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B401" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C401" s="4">
+        <v>45844.0</v>
+      </c>
+      <c r="D401" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="E401" s="5">
+        <v>-0.95</v>
+      </c>
+      <c r="F401" s="5">
+        <v>0.8068481443</v>
+      </c>
+      <c r="G401" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B402" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C402" s="4">
+        <v>45837.0</v>
+      </c>
+      <c r="D402" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E402" s="5">
+        <v>-1.22</v>
+      </c>
+      <c r="F402" s="5">
+        <v>0.767655746</v>
+      </c>
+      <c r="G402" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B403" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C403" s="4">
+        <v>45816.0</v>
+      </c>
+      <c r="D403" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E403" s="5">
+        <v>-1.14</v>
+      </c>
+      <c r="F403" s="5">
+        <v>0.77256111</v>
+      </c>
+      <c r="G403" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B404" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C404" s="4">
+        <v>45809.0</v>
+      </c>
+      <c r="D404" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="E404" s="5">
+        <v>-1.24</v>
+      </c>
+      <c r="F404" s="5">
+        <v>0.784621423</v>
+      </c>
+      <c r="G404" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B405" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C405" s="4">
+        <v>45802.0</v>
+      </c>
+      <c r="D405" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="E405" s="5">
+        <v>-1.16</v>
+      </c>
+      <c r="F405" s="5">
+        <v>0.794731133</v>
+      </c>
+      <c r="G405" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B406" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C406" s="4">
+        <v>45788.0</v>
+      </c>
+      <c r="D406" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E406" s="5">
+        <v>-1.44</v>
+      </c>
+      <c r="F406" s="5">
+        <v>0.766630935</v>
+      </c>
+      <c r="G406" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B407" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C407" s="4">
+        <v>45774.0</v>
+      </c>
+      <c r="D407" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="E407" s="5">
+        <v>-1.58</v>
+      </c>
+      <c r="F407" s="5">
+        <v>0.767580955</v>
+      </c>
+      <c r="G407" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B408" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C408" s="4">
+        <v>45767.0</v>
+      </c>
+      <c r="D408" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="E408" s="5">
+        <v>-1.78</v>
+      </c>
+      <c r="F408" s="5">
+        <v>0.7763861254</v>
+      </c>
+      <c r="G408" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B409" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C409" s="4">
+        <v>45746.0</v>
+      </c>
+      <c r="D409" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="E409" s="5">
+        <v>-1.39</v>
+      </c>
+      <c r="F409" s="5">
+        <v>0.756460944</v>
+      </c>
+      <c r="G409" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B410" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C410" s="4">
+        <v>45739.0</v>
+      </c>
+      <c r="D410" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E410" s="5">
+        <v>-0.9</v>
+      </c>
+      <c r="F410" s="5">
+        <v>0.7986621354</v>
+      </c>
+      <c r="G410" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B411" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C411" s="4">
+        <v>45725.0</v>
+      </c>
+      <c r="D411" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="E411" s="5">
+        <v>-1.66</v>
+      </c>
+      <c r="F411" s="5">
+        <v>0.745586105</v>
+      </c>
+      <c r="G411" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B412" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C412" s="4">
+        <v>45711.0</v>
+      </c>
+      <c r="D412" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="E412" s="5">
+        <v>-1.86</v>
+      </c>
+      <c r="F412" s="5">
+        <v>0.723010415</v>
+      </c>
+      <c r="G412" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B413" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C413" s="4">
+        <v>45697.0</v>
+      </c>
+      <c r="D413" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="E413" s="5">
+        <v>-1.06</v>
+      </c>
+      <c r="F413" s="5">
+        <v>0.785228829</v>
+      </c>
+      <c r="G413" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B414" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C414" s="4">
+        <v>45690.0</v>
+      </c>
+      <c r="D414" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="E414" s="5">
+        <v>-0.9</v>
+      </c>
+      <c r="F414" s="5">
+        <v>0.809883361</v>
+      </c>
+      <c r="G414" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B415" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C415" s="4">
+        <v>45683.0</v>
+      </c>
+      <c r="D415" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="E415" s="5">
+        <v>-0.84</v>
+      </c>
+      <c r="F415" s="5">
+        <v>0.8115167</v>
+      </c>
+      <c r="G415" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B416" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C416" s="4">
+        <v>45676.0</v>
+      </c>
+      <c r="D416" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="E416" s="5">
+        <v>-0.43</v>
+      </c>
+      <c r="F416" s="5">
+        <v>0.8938384841</v>
+      </c>
+      <c r="G416" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B417" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C417" s="4">
+        <v>45648.0</v>
+      </c>
+      <c r="D417" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="E417" s="5">
+        <v>-1.71</v>
+      </c>
+      <c r="F417" s="5">
+        <v>0.708378054</v>
+      </c>
+      <c r="G417" s="5">
+        <v>2024.0</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B418" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C418" s="4">
+        <v>45641.0</v>
+      </c>
+      <c r="D418" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="E418" s="5">
+        <v>-1.52</v>
+      </c>
+      <c r="F418" s="5">
+        <v>0.7996961068</v>
+      </c>
+      <c r="G418" s="5">
+        <v>2024.0</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B419" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C419" s="4">
+        <v>45634.0</v>
+      </c>
+      <c r="D419" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="E419" s="5">
+        <v>-0.31</v>
+      </c>
+      <c r="F419" s="5">
+        <v>0.8184971766</v>
+      </c>
+      <c r="G419" s="5">
+        <v>2024.0</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B420" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C420" s="4">
+        <v>45627.0</v>
+      </c>
+      <c r="D420" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="E420" s="5">
+        <v>-1.95</v>
+      </c>
+      <c r="F420" s="5">
+        <v>0.7550681444</v>
+      </c>
+      <c r="G420" s="5">
+        <v>2024.0</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B421" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C421" s="4">
+        <v>45620.0</v>
+      </c>
+      <c r="D421" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E421" s="5">
+        <v>-2.0</v>
+      </c>
+      <c r="F421" s="5">
+        <v>0.734561221</v>
+      </c>
+      <c r="G421" s="5">
+        <v>2024.0</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B422" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="C422" s="4">
+        <v>45886.0</v>
+      </c>
+      <c r="D422" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="E422" s="5">
+        <v>-0.17</v>
+      </c>
+      <c r="F422" s="5">
+        <v>0.847405433</v>
+      </c>
+      <c r="G422" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B423" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C423" s="4">
+        <v>45879.0</v>
+      </c>
+      <c r="D423" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="E423" s="5">
+        <v>-0.19</v>
+      </c>
+      <c r="F423" s="5">
+        <v>0.8586665268</v>
+      </c>
+      <c r="G423" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B424" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C424" s="4">
+        <v>45865.0</v>
+      </c>
+      <c r="D424" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="E424" s="5">
+        <v>-0.18</v>
+      </c>
+      <c r="F424" s="5">
+        <v>0.85117024</v>
+      </c>
+      <c r="G424" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B425" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C425" s="4">
+        <v>45851.0</v>
+      </c>
+      <c r="D425" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="E425" s="5">
+        <v>-0.19</v>
+      </c>
+      <c r="F425" s="5">
+        <v>0.8636455445</v>
+      </c>
+      <c r="G425" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B426" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="C426" s="4">
+        <v>45837.0</v>
+      </c>
+      <c r="D426" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="E426" s="5">
+        <v>-0.19</v>
+      </c>
+      <c r="F426" s="5">
+        <v>0.8637825859</v>
+      </c>
+      <c r="G426" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B427" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="C427" s="4">
+        <v>45816.0</v>
+      </c>
+      <c r="D427" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="E427" s="5">
+        <v>-0.18</v>
+      </c>
+      <c r="F427" s="5">
+        <v>0.8665555859</v>
+      </c>
+      <c r="G427" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B428" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C428" s="4">
+        <v>45781.0</v>
+      </c>
+      <c r="D428" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="E428" s="5">
+        <v>-0.1</v>
+      </c>
+      <c r="F428" s="5">
+        <v>0.879127833</v>
+      </c>
+      <c r="G428" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B429" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C429" s="4">
+        <v>45774.0</v>
+      </c>
+      <c r="D429" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="E429" s="5">
+        <v>-0.05</v>
+      </c>
+      <c r="F429" s="5">
+        <v>0.8712178839</v>
+      </c>
+      <c r="G429" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B430" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C430" s="4">
+        <v>45753.0</v>
+      </c>
+      <c r="D430" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="E430" s="5">
+        <v>-0.08</v>
+      </c>
+      <c r="F430" s="5">
+        <v>0.8632525747</v>
+      </c>
+      <c r="G430" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B431" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C431" s="4">
+        <v>45732.0</v>
+      </c>
+      <c r="D431" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="E431" s="5">
+        <v>-0.09</v>
+      </c>
+      <c r="F431" s="5">
+        <v>0.85226122</v>
+      </c>
+      <c r="G431" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B432" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C432" s="4">
+        <v>45725.0</v>
+      </c>
+      <c r="D432" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E432" s="5">
+        <v>-0.11</v>
+      </c>
+      <c r="F432" s="5">
+        <v>0.85954118</v>
+      </c>
+      <c r="G432" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B433" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C433" s="4">
+        <v>45704.0</v>
+      </c>
+      <c r="D433" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="E433" s="5">
+        <v>-0.12</v>
+      </c>
+      <c r="F433" s="5">
+        <v>0.8526465141</v>
+      </c>
+      <c r="G433" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B434" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="C434" s="4">
+        <v>45696.0</v>
+      </c>
+      <c r="D434" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="E434" s="5">
+        <v>-0.12</v>
+      </c>
+      <c r="F434" s="5">
+        <v>0.851736363</v>
+      </c>
+      <c r="G434" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B435" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C435" s="4">
+        <v>45858.0</v>
+      </c>
+      <c r="D435" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="E435" s="5">
+        <v>0.02</v>
+      </c>
+      <c r="F435" s="5">
+        <v>0.96529835</v>
+      </c>
+      <c r="G435" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B436" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C436" s="4">
+        <v>45823.0</v>
+      </c>
+      <c r="D436" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="E436" s="5">
+        <v>-0.08</v>
+      </c>
+      <c r="F436" s="5">
+        <v>0.9676987483</v>
+      </c>
+      <c r="G436" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B437" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C437" s="4">
+        <v>45795.0</v>
+      </c>
+      <c r="D437" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="E437" s="5">
+        <v>-0.04</v>
+      </c>
+      <c r="F437" s="5">
+        <v>0.9613289345</v>
+      </c>
+      <c r="G437" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B438" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C438" s="4">
+        <v>45760.0</v>
+      </c>
+      <c r="D438" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="E438" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="F438" s="5">
+        <v>0.9518909367</v>
+      </c>
+      <c r="G438" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B439" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C439" s="4">
+        <v>45998.0</v>
+      </c>
+      <c r="D439" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E439" s="5">
+        <v>1.06</v>
+      </c>
+      <c r="F439" s="5">
+        <v>0.8921889568</v>
+      </c>
+      <c r="G439" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B440" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C440" s="4">
+        <v>45984.0</v>
+      </c>
+      <c r="D440" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="E440" s="5">
+        <v>-0.44</v>
+      </c>
+      <c r="F440" s="5">
+        <v>0.8848402839</v>
+      </c>
+      <c r="G440" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B441" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C441" s="4">
+        <v>45977.0</v>
+      </c>
+      <c r="D441" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="E441" s="5">
+        <v>-0.66</v>
+      </c>
+      <c r="F441" s="5">
+        <v>0.8594941668</v>
+      </c>
+      <c r="G441" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B442" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C442" s="4">
+        <v>45970.0</v>
+      </c>
+      <c r="D442" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="E442" s="5">
+        <v>-0.42</v>
+      </c>
+      <c r="F442" s="5">
+        <v>0.8769612853</v>
+      </c>
+      <c r="G442" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B443" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="C443" s="4">
+        <v>45956.0</v>
+      </c>
+      <c r="D443" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="E443" s="5">
+        <v>-0.43</v>
+      </c>
+      <c r="F443" s="5">
+        <v>0.8728222726</v>
+      </c>
+      <c r="G443" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B444" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C444" s="4">
+        <v>45942.0</v>
+      </c>
+      <c r="D444" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="E444" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="F444" s="5">
+        <v>0.8859704959</v>
+      </c>
+      <c r="G444" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B445" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C445" s="4">
+        <v>45935.0</v>
+      </c>
+      <c r="D445" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="E445" s="5">
+        <v>-0.35</v>
+      </c>
+      <c r="F445" s="5">
+        <v>0.8774662154</v>
+      </c>
+      <c r="G445" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B446" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C446" s="4">
+        <v>45914.0</v>
+      </c>
+      <c r="D446" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="E446" s="5">
+        <v>-0.34</v>
+      </c>
+      <c r="F446" s="5">
+        <v>0.9335668963</v>
+      </c>
+      <c r="G446" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B447" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C447" s="4">
+        <v>45893.0</v>
+      </c>
+      <c r="D447" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="E447" s="5">
+        <v>1.32</v>
+      </c>
+      <c r="F447" s="5">
+        <v>0.9418579857</v>
+      </c>
+      <c r="G447" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B448" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C448" s="4">
+        <v>45886.0</v>
+      </c>
+      <c r="D448" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="E448" s="5">
+        <v>1.04</v>
+      </c>
+      <c r="F448" s="5">
+        <v>0.9411209642</v>
+      </c>
+      <c r="G448" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B449" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C449" s="4">
+        <v>45879.0</v>
+      </c>
+      <c r="D449" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="E449" s="5">
+        <v>0.81</v>
+      </c>
+      <c r="F449" s="5">
+        <v>0.945471857</v>
+      </c>
+      <c r="G449" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B450" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C450" s="4">
+        <v>45872.0</v>
+      </c>
+      <c r="D450" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="E450" s="5">
+        <v>-0.09</v>
+      </c>
+      <c r="F450" s="5">
+        <v>0.92423915</v>
+      </c>
+      <c r="G450" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B451" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C451" s="4">
+        <v>45865.0</v>
+      </c>
+      <c r="D451" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="E451" s="5">
+        <v>-0.25</v>
+      </c>
+      <c r="F451" s="5">
+        <v>0.9062313844</v>
+      </c>
+      <c r="G451" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B452" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C452" s="4">
+        <v>45851.0</v>
+      </c>
+      <c r="D452" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E452" s="5">
+        <v>-0.99</v>
+      </c>
+      <c r="F452" s="5">
+        <v>0.813442153</v>
+      </c>
+      <c r="G452" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B453" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C453" s="4">
+        <v>45851.0</v>
+      </c>
+      <c r="D453" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E453" s="5">
+        <v>0.06</v>
+      </c>
+      <c r="F453" s="5">
+        <v>0.9485506567</v>
+      </c>
+      <c r="G453" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B454" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C454" s="4">
+        <v>45844.0</v>
+      </c>
+      <c r="D454" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="E454" s="5">
+        <v>-0.33</v>
+      </c>
+      <c r="F454" s="5">
+        <v>0.8999942673</v>
+      </c>
+      <c r="G454" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B455" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="C455" s="4">
+        <v>45837.0</v>
+      </c>
+      <c r="D455" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="E455" s="5">
+        <v>-0.29</v>
+      </c>
+      <c r="F455" s="5">
+        <v>0.9110088378</v>
+      </c>
+      <c r="G455" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B456" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C456" s="4">
+        <v>45830.0</v>
+      </c>
+      <c r="D456" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="E456" s="5">
+        <v>0.81</v>
+      </c>
+      <c r="F456" s="5">
+        <v>0.9524839467</v>
+      </c>
+      <c r="G456" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B457" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C457" s="4">
+        <v>45816.0</v>
+      </c>
+      <c r="D457" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="E457" s="5">
+        <v>-0.45</v>
+      </c>
+      <c r="F457" s="5">
+        <v>0.9198763871</v>
+      </c>
+      <c r="G457" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B458" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C458" s="4">
+        <v>45809.0</v>
+      </c>
+      <c r="D458" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E458" s="5">
+        <v>0.74</v>
+      </c>
+      <c r="F458" s="5">
+        <v>0.9418179543</v>
+      </c>
+      <c r="G458" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B459" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C459" s="4">
+        <v>45802.0</v>
+      </c>
+      <c r="D459" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="E459" s="5">
+        <v>0.01</v>
+      </c>
+      <c r="F459" s="5">
+        <v>0.9322226336</v>
+      </c>
+      <c r="G459" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B460" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C460" s="4">
+        <v>45788.0</v>
+      </c>
+      <c r="D460" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="E460" s="5">
+        <v>-0.6</v>
+      </c>
+      <c r="F460" s="5">
+        <v>0.8595692061</v>
+      </c>
+      <c r="G460" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B461" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C461" s="4">
+        <v>45788.0</v>
+      </c>
+      <c r="D461" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="E461" s="5">
+        <v>0.72</v>
+      </c>
+      <c r="F461" s="5">
+        <v>0.9355567161</v>
+      </c>
+      <c r="G461" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B462" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C462" s="4">
+        <v>45781.0</v>
+      </c>
+      <c r="D462" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="E462" s="5">
+        <v>-0.31</v>
+      </c>
+      <c r="F462" s="5">
+        <v>0.91009632</v>
+      </c>
+      <c r="G462" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B463" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C463" s="4">
+        <v>45767.0</v>
+      </c>
+      <c r="D463" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="E463" s="5">
+        <v>0.76</v>
+      </c>
+      <c r="F463" s="5">
+        <v>0.9487358368</v>
+      </c>
+      <c r="G463" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B464" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C464" s="4">
+        <v>45767.0</v>
+      </c>
+      <c r="D464" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="E464" s="5">
+        <v>-1.0</v>
+      </c>
+      <c r="F464" s="5">
+        <v>0.8262782354</v>
+      </c>
+      <c r="G464" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B465" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C465" s="4">
+        <v>45753.0</v>
+      </c>
+      <c r="D465" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="E465" s="5">
+        <v>-0.2</v>
+      </c>
+      <c r="F465" s="5">
+        <v>0.9138193831</v>
+      </c>
+      <c r="G465" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B466" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C466" s="4">
+        <v>45746.0</v>
+      </c>
+      <c r="D466" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="E466" s="5">
+        <v>-0.13</v>
+      </c>
+      <c r="F466" s="5">
+        <v>0.922576833</v>
+      </c>
+      <c r="G466" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B467" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C467" s="4">
+        <v>45739.0</v>
+      </c>
+      <c r="D467" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="E467" s="5">
+        <v>-0.06</v>
+      </c>
+      <c r="F467" s="5">
+        <v>0.9290725171</v>
+      </c>
+      <c r="G467" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B468" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C468" s="4">
+        <v>45732.0</v>
+      </c>
+      <c r="D468" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="E468" s="5">
+        <v>0.38</v>
+      </c>
+      <c r="F468" s="5">
+        <v>0.9568777774</v>
+      </c>
+      <c r="G468" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B469" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C469" s="4">
+        <v>45725.0</v>
+      </c>
+      <c r="D469" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="E469" s="5">
+        <v>0.77</v>
+      </c>
+      <c r="F469" s="5">
+        <v>0.9451658266</v>
+      </c>
+      <c r="G469" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B470" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C470" s="4">
+        <v>45725.0</v>
+      </c>
+      <c r="D470" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="E470" s="5">
+        <v>-1.0</v>
+      </c>
+      <c r="F470" s="5">
+        <v>0.8164561444</v>
+      </c>
+      <c r="G470" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B471" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C471" s="4">
+        <v>45718.0</v>
+      </c>
+      <c r="D471" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E471" s="5">
+        <v>-0.09</v>
+      </c>
+      <c r="F471" s="5">
+        <v>0.9081393351</v>
+      </c>
+      <c r="G471" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B472" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="C472" s="4">
+        <v>45711.0</v>
+      </c>
+      <c r="D472" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="E472" s="5">
+        <v>-0.46</v>
+      </c>
+      <c r="F472" s="5">
+        <v>0.8775732357</v>
+      </c>
+      <c r="G472" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B473" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C473" s="4">
+        <v>45704.0</v>
+      </c>
+      <c r="D473" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="E473" s="5">
+        <v>0.74</v>
+      </c>
+      <c r="F473" s="5">
+        <v>0.9431948269</v>
+      </c>
+      <c r="G473" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B474" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C474" s="4">
+        <v>45697.0</v>
+      </c>
+      <c r="D474" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="E474" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="F474" s="5">
+        <v>0.9319156533</v>
+      </c>
+      <c r="G474" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B475" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C475" s="4">
+        <v>45690.0</v>
+      </c>
+      <c r="D475" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="E475" s="5">
+        <v>0.71</v>
+      </c>
+      <c r="F475" s="5">
+        <v>0.9443557558</v>
+      </c>
+      <c r="G475" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B476" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C476" s="4">
+        <v>45682.0</v>
+      </c>
+      <c r="D476" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="E476" s="5">
+        <v>-0.22</v>
+      </c>
+      <c r="F476" s="5">
+        <v>0.9160804461</v>
+      </c>
+      <c r="G476" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B477" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C477" s="4">
+        <v>45676.0</v>
+      </c>
+      <c r="D477" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="E477" s="5">
+        <v>-0.12</v>
+      </c>
+      <c r="F477" s="5">
+        <v>0.91138402</v>
+      </c>
+      <c r="G477" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B478" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C478" s="4">
+        <v>45669.0</v>
+      </c>
+      <c r="D478" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="E478" s="5">
+        <v>-0.11</v>
+      </c>
+      <c r="F478" s="5">
+        <v>0.9297863974</v>
+      </c>
+      <c r="G478" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B479" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C479" s="4">
+        <v>45662.0</v>
+      </c>
+      <c r="D479" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="E479" s="5">
+        <v>0.62</v>
+      </c>
+      <c r="F479" s="5">
+        <v>0.9211197435</v>
+      </c>
+      <c r="G479" s="5">
+        <v>2025.0</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B480" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C480" s="2">
+        <v>46040.0</v>
+      </c>
+      <c r="D480" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="E480" s="1">
+        <v>-0.01</v>
+      </c>
+      <c r="F480" s="1">
+        <v>0.91</v>
+      </c>
+      <c r="G480" s="1">
+        <v>2026.0</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B481" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C481" s="2">
+        <v>46040.0</v>
+      </c>
+      <c r="D481" s="1">
+        <v>2026105.0</v>
+      </c>
+      <c r="E481" s="1">
+        <v>-0.63</v>
+      </c>
+      <c r="F481" s="1">
+        <v>0.83</v>
+      </c>
+      <c r="G481" s="1">
+        <v>2026.0</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="$A$1:$Z$481">
+    <sortState ref="A1:Z481">
+      <sortCondition ref="D1:D481"/>
+    </sortState>
+  </autoFilter>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>